--- a/dataset_t6_grouped/results2/G1/G1_T0374L_W0041F0003T0006Z000C1N1_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T0374L_W0041F0003T0006Z000C1N1_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>40.27109219474886</v>
+        <v>6.54405248164669</v>
       </c>
       <c r="D2" t="n">
-        <v>40.13463566448129</v>
+        <v>6.521878295478211</v>
       </c>
       <c r="E2" t="n">
-        <v>7.121097219335542</v>
+        <v>1.157178298142026</v>
       </c>
       <c r="F2" t="n">
-        <v>7.116197016236302</v>
+        <v>1.156382015138399</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>24.5712005073872</v>
+        <v>3.992820082450419</v>
       </c>
       <c r="D3" t="n">
-        <v>24.69300451431149</v>
+        <v>4.012613233575617</v>
       </c>
       <c r="E3" t="n">
-        <v>7.121097219335542</v>
+        <v>1.157178298142026</v>
       </c>
       <c r="F3" t="n">
-        <v>7.116197016236302</v>
+        <v>1.156382015138399</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>41.6997331195427</v>
+        <v>6.776206631925689</v>
       </c>
       <c r="D4" t="n">
-        <v>41.82881286723045</v>
+        <v>6.797182090924948</v>
       </c>
       <c r="E4" t="n">
-        <v>7.121097219335542</v>
+        <v>1.157178298142026</v>
       </c>
       <c r="F4" t="n">
-        <v>7.116197016236302</v>
+        <v>1.156382015138399</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>40.95484448884846</v>
+        <v>6.655162229437875</v>
       </c>
       <c r="D5" t="n">
-        <v>41.23772663582367</v>
+        <v>6.701130578321346</v>
       </c>
       <c r="E5" t="n">
-        <v>7.121097219335542</v>
+        <v>1.157178298142026</v>
       </c>
       <c r="F5" t="n">
-        <v>7.116197016236302</v>
+        <v>1.156382015138399</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
